--- a/tests2/Anvesh.xlsx
+++ b/tests2/Anvesh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anand.Gummadilli\Documents\Anand_Details\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/369c40edd623e24e/Documents/PlaywrightDemo/PlaywrightDemo/tests2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C6BB314-4BFC-44AE-BD4F-A654D6C3D3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{4C6BB314-4BFC-44AE-BD4F-A654D6C3D3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D4A4780-723A-4718-A627-5AAE7465D9E0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{147B6599-C5F3-4C20-9670-D864EFFB2C93}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{147B6599-C5F3-4C20-9670-D864EFFB2C93}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,37 +36,28 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>Anvesh</t>
-  </si>
-  <si>
-    <t>Asha</t>
-  </si>
-  <si>
-    <t>Sreyu</t>
-  </si>
-  <si>
-    <t>Lucky</t>
+    <t>asha</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Algerian"/>
+      <family val="5"/>
     </font>
   </fonts>
   <fills count="2">
@@ -89,8 +80,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,50 +417,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C6250A-37D1-42EF-9B6D-0A2375BA4B66}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="11" spans="2:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tests2/Anvesh.xlsx
+++ b/tests2/Anvesh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/369c40edd623e24e/Documents/PlaywrightDemo/PlaywrightDemo/tests2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnandaBabuGummadilli\Documents\Anand_Details\Training\PlaywrightDemo\tests2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{4C6BB314-4BFC-44AE-BD4F-A654D6C3D3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D4A4780-723A-4718-A627-5AAE7465D9E0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD7444D-2C16-44CD-9559-BDAF0F4F18E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{147B6599-C5F3-4C20-9670-D864EFFB2C93}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{147B6599-C5F3-4C20-9670-D864EFFB2C93}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,9 +36,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>asha</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>Anvesh</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>Asha</t>
+  </si>
+  <si>
+    <t>Beeramguda</t>
+  </si>
+  <si>
+    <t>Anand</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>Mike</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>Steve</t>
+  </si>
+  <si>
+    <t>Irving</t>
   </si>
 </sst>
 </file>
@@ -417,13 +444,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C6250A-37D1-42EF-9B6D-0A2375BA4B66}">
-  <dimension ref="B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="11" spans="2:2" ht="15" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.4">
+      <c r="B11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests2/Anvesh.xlsx
+++ b/tests2/Anvesh.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/369c40edd623e24e/Documents/PlaywrightDemo/PlaywrightDemo/tests2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/369C40EDD623E24E/Documents/PlaywrightDemo/PlaywrightDemo/tests2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{4C6BB314-4BFC-44AE-BD4F-A654D6C3D3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D4A4780-723A-4718-A627-5AAE7465D9E0}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{4C6BB314-4BFC-44AE-BD4F-A654D6C3D3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D1E8399-AD84-4B1F-8C77-42E4637415AF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{147B6599-C5F3-4C20-9670-D864EFFB2C93}"/>
   </bookViews>
@@ -36,16 +36,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>asha</t>
+  </si>
+  <si>
+    <t>anand</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,6 +64,12 @@
       <color theme="1"/>
       <name val="Algerian"/>
       <family val="5"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Abadi"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -80,9 +92,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,12 +430,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C6250A-37D1-42EF-9B6D-0A2375BA4B66}">
-  <dimension ref="B11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="11" spans="2:2" ht="15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/tests2/Anvesh.xlsx
+++ b/tests2/Anvesh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnandaBabuGummadilli\Documents\Anand_Details\Training\PlaywrightDemo\tests2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/369C40EDD623E24E/Documents/PlaywrightDemo/PlaywrightDemo/tests2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD7444D-2C16-44CD-9559-BDAF0F4F18E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{1CD7444D-2C16-44CD-9559-BDAF0F4F18E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61968475-37ED-4C3D-B36A-A923749EF7EF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{147B6599-C5F3-4C20-9670-D864EFFB2C93}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{147B6599-C5F3-4C20-9670-D864EFFB2C93}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,36 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>Anvesh</t>
+    <t>as</t>
   </si>
   <si>
-    <t>Hyderabad</t>
-  </si>
-  <si>
-    <t>Asha</t>
-  </si>
-  <si>
-    <t>Beeramguda</t>
-  </si>
-  <si>
-    <t>Anand</t>
-  </si>
-  <si>
-    <t>Bangalore</t>
-  </si>
-  <si>
-    <t>Mike</t>
-  </si>
-  <si>
-    <t>Dallas</t>
-  </si>
-  <si>
-    <t>Steve</t>
-  </si>
-  <si>
-    <t>Irving</t>
+    <t>uiopsdfghjikop[]ertyuiop[]\7werty7u890-1qwerghjkp[]\</t>
   </si>
 </sst>
 </file>
@@ -125,6 +101,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,50 +424,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C6250A-37D1-42EF-9B6D-0A2375BA4B66}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="B11" s="1"/>
     </row>
   </sheetData>
